--- a/Files/TestFiles/DraftPicks.xlsx
+++ b/Files/TestFiles/DraftPicks.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/40f61192ff96ff75/Documents/Git/MaddenDraftTool/Files/TestFiles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="54" documentId="11_173B6F532364FF18F55B1250EA3161BA935D9788" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4CBEFFE2-3FDD-4AB0-B23E-485BA1106C17}"/>
+  <xr:revisionPtr revIDLastSave="166" documentId="11_173B6F532364FF18F55B1250EA3161BA935D9788" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{418748E8-5542-453B-85A9-D956A68E7C09}"/>
   <bookViews>
-    <workbookView xWindow="13050" yWindow="0" windowWidth="15855" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$673</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$705</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -205,6 +205,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -530,12 +534,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F705"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="33.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -555,7 +559,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -572,10 +576,10 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -592,10 +596,10 @@
         <v>1</v>
       </c>
       <c r="F3">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -612,10 +616,10 @@
         <v>2</v>
       </c>
       <c r="F4">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -632,10 +636,10 @@
         <v>3</v>
       </c>
       <c r="F5">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -652,10 +656,10 @@
         <v>4</v>
       </c>
       <c r="F6">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -672,10 +676,10 @@
         <v>5</v>
       </c>
       <c r="F7">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -692,10 +696,10 @@
         <v>6</v>
       </c>
       <c r="F8">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -715,7 +719,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -735,7 +739,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -755,7 +759,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -775,7 +779,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -795,7 +799,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -815,7 +819,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -835,7 +839,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>6</v>
       </c>
@@ -855,7 +859,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -875,7 +879,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>6</v>
       </c>
@@ -895,7 +899,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>6</v>
       </c>
@@ -915,7 +919,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>6</v>
       </c>
@@ -935,7 +939,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -955,7 +959,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -975,7 +979,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>6</v>
       </c>
@@ -992,10 +996,10 @@
         <v>0</v>
       </c>
       <c r="F23">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -1012,10 +1016,10 @@
         <v>1</v>
       </c>
       <c r="F24">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>6</v>
       </c>
@@ -1032,10 +1036,10 @@
         <v>2</v>
       </c>
       <c r="F25">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>6</v>
       </c>
@@ -1052,10 +1056,10 @@
         <v>3</v>
       </c>
       <c r="F26">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>6</v>
       </c>
@@ -1072,10 +1076,10 @@
         <v>4</v>
       </c>
       <c r="F27">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>6</v>
       </c>
@@ -1092,10 +1096,10 @@
         <v>5</v>
       </c>
       <c r="F28">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>6</v>
       </c>
@@ -1112,10 +1116,10 @@
         <v>6</v>
       </c>
       <c r="F29">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>6</v>
       </c>
@@ -1135,7 +1139,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>6</v>
       </c>
@@ -1155,7 +1159,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>6</v>
       </c>
@@ -1175,7 +1179,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>6</v>
       </c>
@@ -1195,7 +1199,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>6</v>
       </c>
@@ -1215,7 +1219,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>6</v>
       </c>
@@ -1235,7 +1239,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>6</v>
       </c>
@@ -1255,7 +1259,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>6</v>
       </c>
@@ -1275,7 +1279,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>6</v>
       </c>
@@ -1295,7 +1299,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>6</v>
       </c>
@@ -1315,7 +1319,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>6</v>
       </c>
@@ -1335,7 +1339,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>6</v>
       </c>
@@ -1355,7 +1359,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>6</v>
       </c>
@@ -1375,7 +1379,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>6</v>
       </c>
@@ -1395,7 +1399,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>6</v>
       </c>
@@ -1412,10 +1416,10 @@
         <v>0</v>
       </c>
       <c r="F44">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>6</v>
       </c>
@@ -1432,10 +1436,10 @@
         <v>1</v>
       </c>
       <c r="F45">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>6</v>
       </c>
@@ -1452,10 +1456,10 @@
         <v>2</v>
       </c>
       <c r="F46">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>6</v>
       </c>
@@ -1472,10 +1476,10 @@
         <v>3</v>
       </c>
       <c r="F47">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>6</v>
       </c>
@@ -1492,10 +1496,10 @@
         <v>4</v>
       </c>
       <c r="F48">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>6</v>
       </c>
@@ -1512,10 +1516,10 @@
         <v>5</v>
       </c>
       <c r="F49">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>6</v>
       </c>
@@ -1532,10 +1536,10 @@
         <v>6</v>
       </c>
       <c r="F50">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>6</v>
       </c>
@@ -1555,7 +1559,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>6</v>
       </c>
@@ -1575,7 +1579,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>6</v>
       </c>
@@ -1595,7 +1599,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>6</v>
       </c>
@@ -1615,7 +1619,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>6</v>
       </c>
@@ -1635,7 +1639,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>6</v>
       </c>
@@ -1655,7 +1659,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>6</v>
       </c>
@@ -1675,7 +1679,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>6</v>
       </c>
@@ -1695,7 +1699,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>6</v>
       </c>
@@ -1715,7 +1719,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>6</v>
       </c>
@@ -1735,7 +1739,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>6</v>
       </c>
@@ -1755,7 +1759,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>6</v>
       </c>
@@ -1775,7 +1779,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="63" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>6</v>
       </c>
@@ -1795,7 +1799,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="64" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>6</v>
       </c>
@@ -1815,7 +1819,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>6</v>
       </c>
@@ -1832,10 +1836,10 @@
         <v>0</v>
       </c>
       <c r="F65">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>6</v>
       </c>
@@ -1852,10 +1856,10 @@
         <v>1</v>
       </c>
       <c r="F66">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>6</v>
       </c>
@@ -1872,10 +1876,10 @@
         <v>2</v>
       </c>
       <c r="F67">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>6</v>
       </c>
@@ -1892,10 +1896,10 @@
         <v>3</v>
       </c>
       <c r="F68">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>6</v>
       </c>
@@ -1912,10 +1916,10 @@
         <v>4</v>
       </c>
       <c r="F69">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>6</v>
       </c>
@@ -1932,10 +1936,10 @@
         <v>5</v>
       </c>
       <c r="F70">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>6</v>
       </c>
@@ -1952,10 +1956,10 @@
         <v>6</v>
       </c>
       <c r="F71">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>6</v>
       </c>
@@ -1975,7 +1979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>6</v>
       </c>
@@ -1995,7 +1999,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>6</v>
       </c>
@@ -2015,7 +2019,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>6</v>
       </c>
@@ -2035,7 +2039,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="76" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>6</v>
       </c>
@@ -2055,7 +2059,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>6</v>
       </c>
@@ -2075,7 +2079,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>6</v>
       </c>
@@ -2095,7 +2099,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>6</v>
       </c>
@@ -2115,7 +2119,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="80" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>6</v>
       </c>
@@ -2135,7 +2139,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>6</v>
       </c>
@@ -2155,7 +2159,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="82" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>6</v>
       </c>
@@ -2175,7 +2179,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="83" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>6</v>
       </c>
@@ -2195,7 +2199,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>6</v>
       </c>
@@ -2215,7 +2219,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="85" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>6</v>
       </c>
@@ -2235,7 +2239,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="86" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>6</v>
       </c>
@@ -2252,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="F86">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>6</v>
       </c>
@@ -2272,10 +2276,10 @@
         <v>1</v>
       </c>
       <c r="F87">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>6</v>
       </c>
@@ -2292,10 +2296,10 @@
         <v>2</v>
       </c>
       <c r="F88">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>6</v>
       </c>
@@ -2312,10 +2316,10 @@
         <v>3</v>
       </c>
       <c r="F89">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>6</v>
       </c>
@@ -2332,10 +2336,10 @@
         <v>4</v>
       </c>
       <c r="F90">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>6</v>
       </c>
@@ -2352,10 +2356,10 @@
         <v>5</v>
       </c>
       <c r="F91">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>6</v>
       </c>
@@ -2372,10 +2376,10 @@
         <v>6</v>
       </c>
       <c r="F92">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>6</v>
       </c>
@@ -2395,7 +2399,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>6</v>
       </c>
@@ -2415,7 +2419,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>6</v>
       </c>
@@ -2435,7 +2439,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="96" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>6</v>
       </c>
@@ -2455,7 +2459,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="97" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>6</v>
       </c>
@@ -2475,7 +2479,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>6</v>
       </c>
@@ -2495,7 +2499,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="99" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>6</v>
       </c>
@@ -2515,7 +2519,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="100" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>6</v>
       </c>
@@ -2535,7 +2539,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>6</v>
       </c>
@@ -2555,7 +2559,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>6</v>
       </c>
@@ -2575,7 +2579,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="103" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>6</v>
       </c>
@@ -2595,7 +2599,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="104" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>6</v>
       </c>
@@ -2615,7 +2619,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="105" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>6</v>
       </c>
@@ -2635,7 +2639,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>6</v>
       </c>
@@ -2655,7 +2659,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="107" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>6</v>
       </c>
@@ -2672,10 +2676,10 @@
         <v>0</v>
       </c>
       <c r="F107">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>6</v>
       </c>
@@ -2692,10 +2696,10 @@
         <v>1</v>
       </c>
       <c r="F108">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>6</v>
       </c>
@@ -2712,10 +2716,10 @@
         <v>2</v>
       </c>
       <c r="F109">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>6</v>
       </c>
@@ -2732,10 +2736,10 @@
         <v>3</v>
       </c>
       <c r="F110">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>6</v>
       </c>
@@ -2752,10 +2756,10 @@
         <v>4</v>
       </c>
       <c r="F111">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>6</v>
       </c>
@@ -2772,10 +2776,10 @@
         <v>5</v>
       </c>
       <c r="F112">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>6</v>
       </c>
@@ -2792,10 +2796,10 @@
         <v>6</v>
       </c>
       <c r="F113">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>6</v>
       </c>
@@ -2815,7 +2819,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="115" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>6</v>
       </c>
@@ -2835,7 +2839,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>6</v>
       </c>
@@ -2855,7 +2859,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="117" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>6</v>
       </c>
@@ -2875,7 +2879,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="118" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>6</v>
       </c>
@@ -2895,7 +2899,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>6</v>
       </c>
@@ -2915,7 +2919,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="120" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>6</v>
       </c>
@@ -2935,7 +2939,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>6</v>
       </c>
@@ -2955,7 +2959,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="122" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>6</v>
       </c>
@@ -2975,7 +2979,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="123" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>6</v>
       </c>
@@ -2995,7 +2999,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="124" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>6</v>
       </c>
@@ -3015,7 +3019,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="125" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>6</v>
       </c>
@@ -3035,7 +3039,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="126" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>6</v>
       </c>
@@ -3055,7 +3059,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="127" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>6</v>
       </c>
@@ -3075,7 +3079,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="128" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>6</v>
       </c>
@@ -3092,10 +3096,10 @@
         <v>0</v>
       </c>
       <c r="F128">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>6</v>
       </c>
@@ -3112,10 +3116,10 @@
         <v>1</v>
       </c>
       <c r="F129">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>6</v>
       </c>
@@ -3132,10 +3136,10 @@
         <v>2</v>
       </c>
       <c r="F130">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>6</v>
       </c>
@@ -3152,10 +3156,10 @@
         <v>3</v>
       </c>
       <c r="F131">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>6</v>
       </c>
@@ -3172,10 +3176,10 @@
         <v>4</v>
       </c>
       <c r="F132">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>6</v>
       </c>
@@ -3192,10 +3196,10 @@
         <v>5</v>
       </c>
       <c r="F133">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>6</v>
       </c>
@@ -3212,10 +3216,10 @@
         <v>6</v>
       </c>
       <c r="F134">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>6</v>
       </c>
@@ -3235,7 +3239,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="136" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>6</v>
       </c>
@@ -3255,7 +3259,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="137" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>6</v>
       </c>
@@ -3275,7 +3279,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="138" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>6</v>
       </c>
@@ -3295,7 +3299,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="139" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>6</v>
       </c>
@@ -3315,7 +3319,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="140" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>6</v>
       </c>
@@ -3335,7 +3339,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="141" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>6</v>
       </c>
@@ -3355,7 +3359,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="142" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>6</v>
       </c>
@@ -3375,7 +3379,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="143" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>6</v>
       </c>
@@ -3395,7 +3399,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="144" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>6</v>
       </c>
@@ -3415,7 +3419,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="145" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>6</v>
       </c>
@@ -3435,7 +3439,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="146" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>6</v>
       </c>
@@ -3455,7 +3459,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="147" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>6</v>
       </c>
@@ -3475,7 +3479,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="148" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>6</v>
       </c>
@@ -3495,7 +3499,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="149" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>6</v>
       </c>
@@ -3512,10 +3516,10 @@
         <v>0</v>
       </c>
       <c r="F149">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>6</v>
       </c>
@@ -3532,10 +3536,10 @@
         <v>1</v>
       </c>
       <c r="F150">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>6</v>
       </c>
@@ -3552,10 +3556,10 @@
         <v>2</v>
       </c>
       <c r="F151">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>6</v>
       </c>
@@ -3572,10 +3576,10 @@
         <v>3</v>
       </c>
       <c r="F152">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>6</v>
       </c>
@@ -3592,10 +3596,10 @@
         <v>4</v>
       </c>
       <c r="F153">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>6</v>
       </c>
@@ -3612,10 +3616,10 @@
         <v>5</v>
       </c>
       <c r="F154">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>6</v>
       </c>
@@ -3632,10 +3636,10 @@
         <v>6</v>
       </c>
       <c r="F155">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>6</v>
       </c>
@@ -3655,7 +3659,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="157" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>6</v>
       </c>
@@ -3675,7 +3679,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>6</v>
       </c>
@@ -3695,7 +3699,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="159" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>6</v>
       </c>
@@ -3715,7 +3719,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="160" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>6</v>
       </c>
@@ -3735,7 +3739,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="161" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>6</v>
       </c>
@@ -3755,7 +3759,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="162" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>6</v>
       </c>
@@ -3775,7 +3779,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="163" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>6</v>
       </c>
@@ -3795,7 +3799,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="164" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>6</v>
       </c>
@@ -3815,7 +3819,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="165" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>6</v>
       </c>
@@ -3835,7 +3839,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="166" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>6</v>
       </c>
@@ -3855,7 +3859,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="167" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>6</v>
       </c>
@@ -3875,7 +3879,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="168" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>6</v>
       </c>
@@ -3895,7 +3899,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="169" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>6</v>
       </c>
@@ -3915,7 +3919,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="170" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>6</v>
       </c>
@@ -3935,7 +3939,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="171" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>6</v>
       </c>
@@ -3955,7 +3959,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="172" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>6</v>
       </c>
@@ -3975,7 +3979,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="173" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>6</v>
       </c>
@@ -3992,10 +3996,10 @@
         <v>3</v>
       </c>
       <c r="F173">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="174" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>6</v>
       </c>
@@ -4015,7 +4019,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="175" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>6</v>
       </c>
@@ -4035,7 +4039,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="176" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>6</v>
       </c>
@@ -4055,7 +4059,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="177" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>6</v>
       </c>
@@ -4075,7 +4079,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="178" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>6</v>
       </c>
@@ -4095,7 +4099,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="179" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>6</v>
       </c>
@@ -4115,7 +4119,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="180" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>6</v>
       </c>
@@ -4135,7 +4139,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="181" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>6</v>
       </c>
@@ -4155,7 +4159,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="182" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>6</v>
       </c>
@@ -4175,7 +4179,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="183" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>6</v>
       </c>
@@ -4195,7 +4199,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="184" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>6</v>
       </c>
@@ -4215,7 +4219,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="185" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>6</v>
       </c>
@@ -4235,7 +4239,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="186" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>6</v>
       </c>
@@ -4255,7 +4259,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="187" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>6</v>
       </c>
@@ -4275,7 +4279,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="188" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>6</v>
       </c>
@@ -4295,7 +4299,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="189" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>6</v>
       </c>
@@ -4315,7 +4319,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="190" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>6</v>
       </c>
@@ -4335,7 +4339,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="191" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>6</v>
       </c>
@@ -4352,10 +4356,10 @@
         <v>0</v>
       </c>
       <c r="F191">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="192" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>6</v>
       </c>
@@ -4372,10 +4376,10 @@
         <v>1</v>
       </c>
       <c r="F192">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="193" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>6</v>
       </c>
@@ -4392,10 +4396,10 @@
         <v>2</v>
       </c>
       <c r="F193">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="194" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>6</v>
       </c>
@@ -4412,10 +4416,10 @@
         <v>3</v>
       </c>
       <c r="F194">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="195" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>6</v>
       </c>
@@ -4432,10 +4436,10 @@
         <v>4</v>
       </c>
       <c r="F195">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="196" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>6</v>
       </c>
@@ -4452,10 +4456,10 @@
         <v>5</v>
       </c>
       <c r="F196">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="197" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>6</v>
       </c>
@@ -4472,10 +4476,10 @@
         <v>6</v>
       </c>
       <c r="F197">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="198" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>6</v>
       </c>
@@ -4495,7 +4499,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="199" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>6</v>
       </c>
@@ -4515,7 +4519,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="200" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>6</v>
       </c>
@@ -4535,7 +4539,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="201" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>6</v>
       </c>
@@ -4555,7 +4559,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="202" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>6</v>
       </c>
@@ -4575,7 +4579,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="203" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>6</v>
       </c>
@@ -4595,7 +4599,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="204" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>6</v>
       </c>
@@ -4615,7 +4619,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="205" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>6</v>
       </c>
@@ -4635,7 +4639,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="206" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>6</v>
       </c>
@@ -4655,7 +4659,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="207" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>6</v>
       </c>
@@ -4675,7 +4679,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="208" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>6</v>
       </c>
@@ -4695,7 +4699,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="209" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>6</v>
       </c>
@@ -4715,7 +4719,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="210" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>6</v>
       </c>
@@ -4735,7 +4739,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="211" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>6</v>
       </c>
@@ -4755,7 +4759,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="212" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>6</v>
       </c>
@@ -4772,10 +4776,10 @@
         <v>0</v>
       </c>
       <c r="F212">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="213" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>6</v>
       </c>
@@ -4792,10 +4796,10 @@
         <v>1</v>
       </c>
       <c r="F213">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="214" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>6</v>
       </c>
@@ -4812,10 +4816,10 @@
         <v>2</v>
       </c>
       <c r="F214">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="215" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>6</v>
       </c>
@@ -4832,10 +4836,10 @@
         <v>3</v>
       </c>
       <c r="F215">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="216" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>6</v>
       </c>
@@ -4852,10 +4856,10 @@
         <v>4</v>
       </c>
       <c r="F216">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="217" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>6</v>
       </c>
@@ -4872,10 +4876,10 @@
         <v>5</v>
       </c>
       <c r="F217">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="218" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>6</v>
       </c>
@@ -4892,10 +4896,10 @@
         <v>6</v>
       </c>
       <c r="F218">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="219" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>6</v>
       </c>
@@ -4915,7 +4919,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="220" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>6</v>
       </c>
@@ -4935,7 +4939,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="221" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>6</v>
       </c>
@@ -4955,7 +4959,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="222" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>6</v>
       </c>
@@ -4975,7 +4979,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="223" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>6</v>
       </c>
@@ -4995,7 +4999,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="224" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>6</v>
       </c>
@@ -5015,7 +5019,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="225" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>6</v>
       </c>
@@ -5035,7 +5039,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="226" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>6</v>
       </c>
@@ -5055,7 +5059,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="227" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>6</v>
       </c>
@@ -5075,7 +5079,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="228" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>6</v>
       </c>
@@ -5095,7 +5099,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="229" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>6</v>
       </c>
@@ -5115,7 +5119,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="230" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>6</v>
       </c>
@@ -5135,7 +5139,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="231" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>6</v>
       </c>
@@ -5155,7 +5159,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="232" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>6</v>
       </c>
@@ -5175,7 +5179,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="233" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>6</v>
       </c>
@@ -5192,10 +5196,10 @@
         <v>0</v>
       </c>
       <c r="F233">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="234" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>6</v>
       </c>
@@ -5212,10 +5216,10 @@
         <v>1</v>
       </c>
       <c r="F234">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="235" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>6</v>
       </c>
@@ -5232,10 +5236,10 @@
         <v>2</v>
       </c>
       <c r="F235">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="236" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>6</v>
       </c>
@@ -5252,10 +5256,10 @@
         <v>3</v>
       </c>
       <c r="F236">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="237" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>6</v>
       </c>
@@ -5272,10 +5276,10 @@
         <v>4</v>
       </c>
       <c r="F237">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="238" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>6</v>
       </c>
@@ -5292,10 +5296,10 @@
         <v>5</v>
       </c>
       <c r="F238">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="239" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>6</v>
       </c>
@@ -5312,10 +5316,10 @@
         <v>6</v>
       </c>
       <c r="F239">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="240" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>6</v>
       </c>
@@ -5335,7 +5339,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="241" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>6</v>
       </c>
@@ -5355,7 +5359,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="242" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>6</v>
       </c>
@@ -5375,7 +5379,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="243" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>6</v>
       </c>
@@ -5395,7 +5399,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="244" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>6</v>
       </c>
@@ -5415,7 +5419,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="245" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>6</v>
       </c>
@@ -5435,7 +5439,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="246" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>6</v>
       </c>
@@ -5455,7 +5459,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="247" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>6</v>
       </c>
@@ -5475,7 +5479,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="248" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>6</v>
       </c>
@@ -5495,7 +5499,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="249" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>6</v>
       </c>
@@ -5515,7 +5519,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="250" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>6</v>
       </c>
@@ -5535,7 +5539,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="251" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>6</v>
       </c>
@@ -5555,7 +5559,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="252" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>6</v>
       </c>
@@ -5575,7 +5579,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="253" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>6</v>
       </c>
@@ -5595,7 +5599,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="254" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>6</v>
       </c>
@@ -5612,10 +5616,10 @@
         <v>0</v>
       </c>
       <c r="F254">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="255" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>6</v>
       </c>
@@ -5632,10 +5636,10 @@
         <v>1</v>
       </c>
       <c r="F255">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="256" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>6</v>
       </c>
@@ -5652,10 +5656,10 @@
         <v>2</v>
       </c>
       <c r="F256">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="257" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>6</v>
       </c>
@@ -5672,10 +5676,10 @@
         <v>3</v>
       </c>
       <c r="F257">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="258" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>6</v>
       </c>
@@ -5692,10 +5696,10 @@
         <v>4</v>
       </c>
       <c r="F258">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="259" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>6</v>
       </c>
@@ -5712,10 +5716,10 @@
         <v>5</v>
       </c>
       <c r="F259">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="260" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>6</v>
       </c>
@@ -5732,10 +5736,10 @@
         <v>6</v>
       </c>
       <c r="F260">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="261" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>6</v>
       </c>
@@ -5755,7 +5759,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="262" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>6</v>
       </c>
@@ -5775,7 +5779,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="263" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>6</v>
       </c>
@@ -5795,7 +5799,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="264" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>6</v>
       </c>
@@ -5815,7 +5819,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="265" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>6</v>
       </c>
@@ -5835,7 +5839,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="266" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>6</v>
       </c>
@@ -5855,7 +5859,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="267" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>6</v>
       </c>
@@ -5875,7 +5879,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="268" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>6</v>
       </c>
@@ -5895,7 +5899,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="269" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>6</v>
       </c>
@@ -5915,7 +5919,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="270" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>6</v>
       </c>
@@ -5935,7 +5939,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="271" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>6</v>
       </c>
@@ -5955,7 +5959,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="272" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>6</v>
       </c>
@@ -5975,7 +5979,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="273" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>6</v>
       </c>
@@ -5995,7 +5999,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="274" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>6</v>
       </c>
@@ -6015,7 +6019,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="275" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>6</v>
       </c>
@@ -6032,10 +6036,10 @@
         <v>0</v>
       </c>
       <c r="F275">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="276" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>6</v>
       </c>
@@ -6052,10 +6056,10 @@
         <v>1</v>
       </c>
       <c r="F276">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="277" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>6</v>
       </c>
@@ -6072,10 +6076,10 @@
         <v>2</v>
       </c>
       <c r="F277">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="278" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>6</v>
       </c>
@@ -6092,10 +6096,10 @@
         <v>3</v>
       </c>
       <c r="F278">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="279" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>6</v>
       </c>
@@ -6112,10 +6116,10 @@
         <v>4</v>
       </c>
       <c r="F279">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="280" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>6</v>
       </c>
@@ -6132,10 +6136,10 @@
         <v>5</v>
       </c>
       <c r="F280">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="281" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>6</v>
       </c>
@@ -6152,10 +6156,10 @@
         <v>6</v>
       </c>
       <c r="F281">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="282" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>6</v>
       </c>
@@ -6175,7 +6179,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="283" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>6</v>
       </c>
@@ -6195,7 +6199,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="284" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>6</v>
       </c>
@@ -6215,7 +6219,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="285" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>6</v>
       </c>
@@ -6235,7 +6239,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="286" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>6</v>
       </c>
@@ -6255,7 +6259,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="287" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>6</v>
       </c>
@@ -6275,7 +6279,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="288" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>6</v>
       </c>
@@ -6295,7 +6299,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="289" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>6</v>
       </c>
@@ -6315,7 +6319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>6</v>
       </c>
@@ -6335,7 +6339,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="291" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>6</v>
       </c>
@@ -6355,7 +6359,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="292" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>6</v>
       </c>
@@ -6375,7 +6379,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="293" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>6</v>
       </c>
@@ -6395,7 +6399,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="294" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>6</v>
       </c>
@@ -6415,7 +6419,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="295" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>6</v>
       </c>
@@ -6435,7 +6439,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="296" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>6</v>
       </c>
@@ -6452,10 +6456,10 @@
         <v>0</v>
       </c>
       <c r="F296">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="297" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>6</v>
       </c>
@@ -6472,10 +6476,10 @@
         <v>1</v>
       </c>
       <c r="F297">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="298" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>6</v>
       </c>
@@ -6492,10 +6496,10 @@
         <v>2</v>
       </c>
       <c r="F298">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="299" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>6</v>
       </c>
@@ -6512,10 +6516,10 @@
         <v>3</v>
       </c>
       <c r="F299">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="300" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>6</v>
       </c>
@@ -6532,10 +6536,10 @@
         <v>4</v>
       </c>
       <c r="F300">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="301" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>6</v>
       </c>
@@ -6552,10 +6556,10 @@
         <v>5</v>
       </c>
       <c r="F301">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="302" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>6</v>
       </c>
@@ -6572,10 +6576,10 @@
         <v>6</v>
       </c>
       <c r="F302">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="303" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>6</v>
       </c>
@@ -6595,7 +6599,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="304" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>6</v>
       </c>
@@ -6615,7 +6619,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="305" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>6</v>
       </c>
@@ -6635,7 +6639,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="306" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>6</v>
       </c>
@@ -6655,7 +6659,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="307" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>6</v>
       </c>
@@ -6675,7 +6679,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="308" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>6</v>
       </c>
@@ -6695,7 +6699,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="309" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>6</v>
       </c>
@@ -6715,7 +6719,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="310" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>6</v>
       </c>
@@ -6735,7 +6739,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="311" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>6</v>
       </c>
@@ -6755,7 +6759,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="312" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>6</v>
       </c>
@@ -6775,7 +6779,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="313" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>6</v>
       </c>
@@ -6795,7 +6799,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="314" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>6</v>
       </c>
@@ -6815,7 +6819,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="315" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>6</v>
       </c>
@@ -6835,7 +6839,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="316" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>6</v>
       </c>
@@ -6855,7 +6859,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="317" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>6</v>
       </c>
@@ -6872,10 +6876,10 @@
         <v>0</v>
       </c>
       <c r="F317">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="318" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>6</v>
       </c>
@@ -6892,10 +6896,10 @@
         <v>1</v>
       </c>
       <c r="F318">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="319" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>6</v>
       </c>
@@ -6912,10 +6916,10 @@
         <v>2</v>
       </c>
       <c r="F319">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="320" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>6</v>
       </c>
@@ -6932,10 +6936,10 @@
         <v>3</v>
       </c>
       <c r="F320">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="321" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>6</v>
       </c>
@@ -6952,10 +6956,10 @@
         <v>4</v>
       </c>
       <c r="F321">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="322" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="322" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>6</v>
       </c>
@@ -6972,10 +6976,10 @@
         <v>5</v>
       </c>
       <c r="F322">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="323" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="323" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>6</v>
       </c>
@@ -6992,10 +6996,10 @@
         <v>6</v>
       </c>
       <c r="F323">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="324" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>6</v>
       </c>
@@ -7015,7 +7019,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="325" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>6</v>
       </c>
@@ -7035,7 +7039,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="326" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>6</v>
       </c>
@@ -7055,7 +7059,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="327" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>6</v>
       </c>
@@ -7075,7 +7079,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="328" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>6</v>
       </c>
@@ -7095,7 +7099,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="329" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>6</v>
       </c>
@@ -7115,7 +7119,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="330" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>6</v>
       </c>
@@ -7135,7 +7139,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="331" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>6</v>
       </c>
@@ -7155,7 +7159,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="332" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>6</v>
       </c>
@@ -7175,7 +7179,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="333" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>6</v>
       </c>
@@ -7195,7 +7199,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="334" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>6</v>
       </c>
@@ -7215,7 +7219,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="335" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>6</v>
       </c>
@@ -7235,7 +7239,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="336" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>6</v>
       </c>
@@ -7255,7 +7259,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="337" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>6</v>
       </c>
@@ -7275,7 +7279,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="338" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>6</v>
       </c>
@@ -7292,10 +7296,10 @@
         <v>0</v>
       </c>
       <c r="F338">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="339" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="339" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>6</v>
       </c>
@@ -7312,10 +7316,10 @@
         <v>1</v>
       </c>
       <c r="F339">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="340" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="340" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>6</v>
       </c>
@@ -7332,10 +7336,10 @@
         <v>2</v>
       </c>
       <c r="F340">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="341" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="341" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>6</v>
       </c>
@@ -7352,10 +7356,10 @@
         <v>3</v>
       </c>
       <c r="F341">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="342" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="342" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>6</v>
       </c>
@@ -7372,10 +7376,10 @@
         <v>4</v>
       </c>
       <c r="F342">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="343" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="343" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>6</v>
       </c>
@@ -7392,10 +7396,10 @@
         <v>5</v>
       </c>
       <c r="F343">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="344" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="344" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>6</v>
       </c>
@@ -7412,10 +7416,10 @@
         <v>6</v>
       </c>
       <c r="F344">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="345" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="345" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>6</v>
       </c>
@@ -7435,7 +7439,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="346" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>6</v>
       </c>
@@ -7455,7 +7459,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="347" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>6</v>
       </c>
@@ -7475,7 +7479,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="348" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>6</v>
       </c>
@@ -7495,7 +7499,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="349" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>6</v>
       </c>
@@ -7515,7 +7519,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="350" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>6</v>
       </c>
@@ -7535,7 +7539,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="351" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>6</v>
       </c>
@@ -7555,7 +7559,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="352" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>6</v>
       </c>
@@ -7575,7 +7579,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="353" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>6</v>
       </c>
@@ -7595,7 +7599,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="354" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>6</v>
       </c>
@@ -7615,7 +7619,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="355" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>6</v>
       </c>
@@ -7635,7 +7639,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="356" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>6</v>
       </c>
@@ -7655,7 +7659,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="357" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>6</v>
       </c>
@@ -7675,7 +7679,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="358" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>6</v>
       </c>
@@ -7695,7 +7699,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="359" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>6</v>
       </c>
@@ -7712,10 +7716,10 @@
         <v>0</v>
       </c>
       <c r="F359">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="360" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="360" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>6</v>
       </c>
@@ -7732,10 +7736,10 @@
         <v>1</v>
       </c>
       <c r="F360">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="361" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="361" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>6</v>
       </c>
@@ -7752,10 +7756,10 @@
         <v>2</v>
       </c>
       <c r="F361">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="362" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="362" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>6</v>
       </c>
@@ -7772,10 +7776,10 @@
         <v>3</v>
       </c>
       <c r="F362">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="363" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="363" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>6</v>
       </c>
@@ -7792,10 +7796,10 @@
         <v>4</v>
       </c>
       <c r="F363">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="364" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="364" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>6</v>
       </c>
@@ -7812,10 +7816,10 @@
         <v>5</v>
       </c>
       <c r="F364">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="365" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="365" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>6</v>
       </c>
@@ -7832,10 +7836,10 @@
         <v>6</v>
       </c>
       <c r="F365">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="366" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="366" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>6</v>
       </c>
@@ -7855,7 +7859,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="367" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>6</v>
       </c>
@@ -7875,7 +7879,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="368" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>6</v>
       </c>
@@ -7895,7 +7899,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="369" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>6</v>
       </c>
@@ -7915,7 +7919,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="370" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>6</v>
       </c>
@@ -7935,7 +7939,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="371" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>6</v>
       </c>
@@ -7955,7 +7959,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="372" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>6</v>
       </c>
@@ -7975,7 +7979,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="373" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>6</v>
       </c>
@@ -7995,7 +7999,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="374" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>6</v>
       </c>
@@ -8015,7 +8019,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="375" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>6</v>
       </c>
@@ -8035,7 +8039,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="376" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>6</v>
       </c>
@@ -8055,7 +8059,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="377" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>6</v>
       </c>
@@ -8075,7 +8079,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="378" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>6</v>
       </c>
@@ -8095,7 +8099,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="379" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>6</v>
       </c>
@@ -8115,7 +8119,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="380" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>6</v>
       </c>
@@ -8132,10 +8136,10 @@
         <v>0</v>
       </c>
       <c r="F380">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="381" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="381" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>6</v>
       </c>
@@ -8152,10 +8156,10 @@
         <v>1</v>
       </c>
       <c r="F381">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="382" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="382" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>6</v>
       </c>
@@ -8172,10 +8176,10 @@
         <v>2</v>
       </c>
       <c r="F382">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="383" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="383" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>6</v>
       </c>
@@ -8192,10 +8196,10 @@
         <v>3</v>
       </c>
       <c r="F383">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="384" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="384" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>6</v>
       </c>
@@ -8212,10 +8216,10 @@
         <v>4</v>
       </c>
       <c r="F384">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="385" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="385" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>6</v>
       </c>
@@ -8232,10 +8236,10 @@
         <v>5</v>
       </c>
       <c r="F385">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="386" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="386" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>6</v>
       </c>
@@ -8252,10 +8256,10 @@
         <v>6</v>
       </c>
       <c r="F386">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="387" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="387" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>6</v>
       </c>
@@ -8275,7 +8279,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="388" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>6</v>
       </c>
@@ -8295,7 +8299,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="389" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>6</v>
       </c>
@@ -8315,7 +8319,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="390" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>6</v>
       </c>
@@ -8335,7 +8339,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="391" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>6</v>
       </c>
@@ -8355,7 +8359,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="392" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>6</v>
       </c>
@@ -8375,7 +8379,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="393" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>6</v>
       </c>
@@ -8395,7 +8399,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="394" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>6</v>
       </c>
@@ -8415,7 +8419,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="395" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>6</v>
       </c>
@@ -8435,7 +8439,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="396" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>6</v>
       </c>
@@ -8455,7 +8459,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="397" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>6</v>
       </c>
@@ -8475,7 +8479,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="398" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>6</v>
       </c>
@@ -8495,7 +8499,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="399" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>6</v>
       </c>
@@ -8515,7 +8519,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="400" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>6</v>
       </c>
@@ -8535,7 +8539,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="401" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>6</v>
       </c>
@@ -8552,10 +8556,10 @@
         <v>0</v>
       </c>
       <c r="F401">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="402" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="402" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>6</v>
       </c>
@@ -8572,10 +8576,10 @@
         <v>1</v>
       </c>
       <c r="F402">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="403" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="403" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>6</v>
       </c>
@@ -8592,10 +8596,10 @@
         <v>2</v>
       </c>
       <c r="F403">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="404" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="404" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>6</v>
       </c>
@@ -8612,10 +8616,10 @@
         <v>3</v>
       </c>
       <c r="F404">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="405" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="405" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>6</v>
       </c>
@@ -8632,10 +8636,10 @@
         <v>4</v>
       </c>
       <c r="F405">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="406" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="406" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>6</v>
       </c>
@@ -8652,10 +8656,10 @@
         <v>5</v>
       </c>
       <c r="F406">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="407" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="407" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>6</v>
       </c>
@@ -8672,10 +8676,10 @@
         <v>6</v>
       </c>
       <c r="F407">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="408" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="408" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>6</v>
       </c>
@@ -8695,7 +8699,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="409" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>6</v>
       </c>
@@ -8715,7 +8719,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="410" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>6</v>
       </c>
@@ -8735,7 +8739,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="411" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>6</v>
       </c>
@@ -8755,7 +8759,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="412" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>6</v>
       </c>
@@ -8775,7 +8779,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="413" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>6</v>
       </c>
@@ -8795,7 +8799,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="414" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>6</v>
       </c>
@@ -8815,7 +8819,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="415" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>6</v>
       </c>
@@ -8835,7 +8839,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="416" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>6</v>
       </c>
@@ -8855,7 +8859,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="417" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>6</v>
       </c>
@@ -8875,7 +8879,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="418" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>6</v>
       </c>
@@ -8895,7 +8899,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="419" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>6</v>
       </c>
@@ -8915,7 +8919,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="420" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>6</v>
       </c>
@@ -8935,7 +8939,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="421" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>6</v>
       </c>
@@ -8955,7 +8959,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="422" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>6</v>
       </c>
@@ -8972,10 +8976,10 @@
         <v>0</v>
       </c>
       <c r="F422">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="423" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="423" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>6</v>
       </c>
@@ -8992,10 +8996,10 @@
         <v>1</v>
       </c>
       <c r="F423">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="424" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="424" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>6</v>
       </c>
@@ -9012,10 +9016,10 @@
         <v>2</v>
       </c>
       <c r="F424">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="425" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="425" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>6</v>
       </c>
@@ -9032,10 +9036,10 @@
         <v>3</v>
       </c>
       <c r="F425">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="426" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="426" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>6</v>
       </c>
@@ -9052,10 +9056,10 @@
         <v>4</v>
       </c>
       <c r="F426">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="427" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="427" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>6</v>
       </c>
@@ -9072,10 +9076,10 @@
         <v>5</v>
       </c>
       <c r="F427">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="428" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="428" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>6</v>
       </c>
@@ -9092,10 +9096,10 @@
         <v>6</v>
       </c>
       <c r="F428">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="429" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="429" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>6</v>
       </c>
@@ -9115,7 +9119,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="430" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>6</v>
       </c>
@@ -9135,7 +9139,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="431" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>6</v>
       </c>
@@ -9155,7 +9159,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="432" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>6</v>
       </c>
@@ -9175,7 +9179,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="433" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>6</v>
       </c>
@@ -9195,7 +9199,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="434" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>6</v>
       </c>
@@ -9215,7 +9219,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="435" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>6</v>
       </c>
@@ -9235,7 +9239,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="436" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>6</v>
       </c>
@@ -9255,7 +9259,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="437" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>6</v>
       </c>
@@ -9275,7 +9279,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="438" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>6</v>
       </c>
@@ -9295,7 +9299,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="439" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>6</v>
       </c>
@@ -9315,7 +9319,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="440" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>6</v>
       </c>
@@ -9335,7 +9339,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="441" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>6</v>
       </c>
@@ -9355,7 +9359,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="442" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>6</v>
       </c>
@@ -9375,7 +9379,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="443" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>6</v>
       </c>
@@ -9392,10 +9396,10 @@
         <v>0</v>
       </c>
       <c r="F443">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="444" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="444" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>6</v>
       </c>
@@ -9412,10 +9416,10 @@
         <v>1</v>
       </c>
       <c r="F444">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="445" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="445" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>6</v>
       </c>
@@ -9432,10 +9436,10 @@
         <v>2</v>
       </c>
       <c r="F445">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="446" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="446" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>6</v>
       </c>
@@ -9452,10 +9456,10 @@
         <v>3</v>
       </c>
       <c r="F446">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="447" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="447" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>6</v>
       </c>
@@ -9472,10 +9476,10 @@
         <v>4</v>
       </c>
       <c r="F447">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="448" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="448" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>6</v>
       </c>
@@ -9492,10 +9496,10 @@
         <v>5</v>
       </c>
       <c r="F448">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="449" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="449" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>6</v>
       </c>
@@ -9512,10 +9516,10 @@
         <v>6</v>
       </c>
       <c r="F449">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="450" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="450" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>6</v>
       </c>
@@ -9535,7 +9539,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="451" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>6</v>
       </c>
@@ -9555,7 +9559,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="452" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>6</v>
       </c>
@@ -9575,7 +9579,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="453" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>6</v>
       </c>
@@ -9595,7 +9599,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="454" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>6</v>
       </c>
@@ -9615,7 +9619,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="455" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>6</v>
       </c>
@@ -9635,7 +9639,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="456" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>6</v>
       </c>
@@ -9655,7 +9659,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="457" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>6</v>
       </c>
@@ -9675,7 +9679,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="458" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>6</v>
       </c>
@@ -9695,7 +9699,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="459" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>6</v>
       </c>
@@ -9715,7 +9719,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="460" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>6</v>
       </c>
@@ -9735,7 +9739,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="461" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>6</v>
       </c>
@@ -9755,7 +9759,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="462" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>6</v>
       </c>
@@ -9775,7 +9779,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="463" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>6</v>
       </c>
@@ -9795,7 +9799,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="464" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>6</v>
       </c>
@@ -9812,10 +9816,10 @@
         <v>0</v>
       </c>
       <c r="F464">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="465" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="465" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>6</v>
       </c>
@@ -9832,10 +9836,10 @@
         <v>1</v>
       </c>
       <c r="F465">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="466" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="466" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>6</v>
       </c>
@@ -9852,10 +9856,10 @@
         <v>2</v>
       </c>
       <c r="F466">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="467" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="467" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>6</v>
       </c>
@@ -9872,10 +9876,10 @@
         <v>3</v>
       </c>
       <c r="F467">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="468" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="468" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>6</v>
       </c>
@@ -9892,10 +9896,10 @@
         <v>4</v>
       </c>
       <c r="F468">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="469" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="469" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>6</v>
       </c>
@@ -9912,10 +9916,10 @@
         <v>5</v>
       </c>
       <c r="F469">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="470" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="470" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>6</v>
       </c>
@@ -9932,10 +9936,10 @@
         <v>6</v>
       </c>
       <c r="F470">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="471" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="471" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>6</v>
       </c>
@@ -9955,7 +9959,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="472" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>6</v>
       </c>
@@ -9975,7 +9979,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="473" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>6</v>
       </c>
@@ -9995,7 +9999,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="474" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>6</v>
       </c>
@@ -10015,7 +10019,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="475" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>6</v>
       </c>
@@ -10035,7 +10039,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="476" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>6</v>
       </c>
@@ -10055,7 +10059,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="477" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>6</v>
       </c>
@@ -10075,7 +10079,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="478" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>6</v>
       </c>
@@ -10095,7 +10099,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="479" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>6</v>
       </c>
@@ -10115,7 +10119,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="480" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>6</v>
       </c>
@@ -10135,7 +10139,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="481" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>6</v>
       </c>
@@ -10155,7 +10159,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="482" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>6</v>
       </c>
@@ -10175,7 +10179,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="483" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>6</v>
       </c>
@@ -10195,7 +10199,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="484" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>6</v>
       </c>
@@ -10215,7 +10219,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="485" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>6</v>
       </c>
@@ -10232,10 +10236,10 @@
         <v>0</v>
       </c>
       <c r="F485">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="486" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="486" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>6</v>
       </c>
@@ -10252,10 +10256,10 @@
         <v>1</v>
       </c>
       <c r="F486">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="487" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="487" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>6</v>
       </c>
@@ -10272,10 +10276,10 @@
         <v>2</v>
       </c>
       <c r="F487">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="488" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="488" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>6</v>
       </c>
@@ -10292,10 +10296,10 @@
         <v>3</v>
       </c>
       <c r="F488">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="489" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="489" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>6</v>
       </c>
@@ -10312,10 +10316,10 @@
         <v>4</v>
       </c>
       <c r="F489">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="490" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="490" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>6</v>
       </c>
@@ -10332,10 +10336,10 @@
         <v>5</v>
       </c>
       <c r="F490">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="491" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="491" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>6</v>
       </c>
@@ -10352,10 +10356,10 @@
         <v>6</v>
       </c>
       <c r="F491">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="492" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="492" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>6</v>
       </c>
@@ -10375,7 +10379,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="493" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>6</v>
       </c>
@@ -10395,7 +10399,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="494" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>6</v>
       </c>
@@ -10415,7 +10419,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="495" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>6</v>
       </c>
@@ -10435,7 +10439,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="496" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>6</v>
       </c>
@@ -10455,7 +10459,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="497" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>6</v>
       </c>
@@ -10475,7 +10479,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="498" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>6</v>
       </c>
@@ -10495,7 +10499,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="499" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>6</v>
       </c>
@@ -10515,7 +10519,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="500" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>6</v>
       </c>
@@ -10535,7 +10539,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="501" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>6</v>
       </c>
@@ -10555,7 +10559,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="502" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>6</v>
       </c>
@@ -10575,7 +10579,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="503" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>6</v>
       </c>
@@ -10595,7 +10599,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="504" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>6</v>
       </c>
@@ -10615,7 +10619,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="505" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>6</v>
       </c>
@@ -10635,7 +10639,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="506" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>6</v>
       </c>
@@ -10652,10 +10656,10 @@
         <v>0</v>
       </c>
       <c r="F506">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="507" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="507" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>6</v>
       </c>
@@ -10672,10 +10676,10 @@
         <v>1</v>
       </c>
       <c r="F507">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="508" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="508" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>6</v>
       </c>
@@ -10692,10 +10696,10 @@
         <v>2</v>
       </c>
       <c r="F508">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="509" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="509" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>6</v>
       </c>
@@ -10712,10 +10716,10 @@
         <v>3</v>
       </c>
       <c r="F509">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="510" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="510" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>6</v>
       </c>
@@ -10732,10 +10736,10 @@
         <v>4</v>
       </c>
       <c r="F510">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="511" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="511" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>6</v>
       </c>
@@ -10752,10 +10756,10 @@
         <v>5</v>
       </c>
       <c r="F511">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="512" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="512" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>6</v>
       </c>
@@ -10772,10 +10776,10 @@
         <v>6</v>
       </c>
       <c r="F512">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="513" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="513" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>6</v>
       </c>
@@ -10795,7 +10799,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="514" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>6</v>
       </c>
@@ -10815,7 +10819,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="515" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>6</v>
       </c>
@@ -10835,7 +10839,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="516" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>6</v>
       </c>
@@ -10855,7 +10859,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="517" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>6</v>
       </c>
@@ -10875,7 +10879,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="518" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>6</v>
       </c>
@@ -10895,7 +10899,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="519" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>6</v>
       </c>
@@ -10915,7 +10919,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="520" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>6</v>
       </c>
@@ -10935,7 +10939,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="521" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>6</v>
       </c>
@@ -10955,7 +10959,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="522" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>6</v>
       </c>
@@ -10975,7 +10979,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="523" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>6</v>
       </c>
@@ -10995,7 +10999,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="524" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>6</v>
       </c>
@@ -11015,7 +11019,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="525" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>6</v>
       </c>
@@ -11035,7 +11039,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="526" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>6</v>
       </c>
@@ -11055,7 +11059,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="527" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>6</v>
       </c>
@@ -11072,10 +11076,10 @@
         <v>0</v>
       </c>
       <c r="F527">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="528" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="528" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>6</v>
       </c>
@@ -11092,10 +11096,10 @@
         <v>1</v>
       </c>
       <c r="F528">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="529" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="529" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
         <v>6</v>
       </c>
@@ -11112,10 +11116,10 @@
         <v>2</v>
       </c>
       <c r="F529">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="530" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="530" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>6</v>
       </c>
@@ -11132,10 +11136,10 @@
         <v>3</v>
       </c>
       <c r="F530">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="531" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="531" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
         <v>6</v>
       </c>
@@ -11152,10 +11156,10 @@
         <v>4</v>
       </c>
       <c r="F531">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="532" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="532" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>6</v>
       </c>
@@ -11172,10 +11176,10 @@
         <v>5</v>
       </c>
       <c r="F532">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="533" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="533" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>6</v>
       </c>
@@ -11192,10 +11196,10 @@
         <v>6</v>
       </c>
       <c r="F533">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="534" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="534" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
         <v>6</v>
       </c>
@@ -11215,7 +11219,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="535" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>6</v>
       </c>
@@ -11235,7 +11239,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="536" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
         <v>6</v>
       </c>
@@ -11255,7 +11259,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="537" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>6</v>
       </c>
@@ -11275,7 +11279,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="538" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>6</v>
       </c>
@@ -11295,7 +11299,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="539" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>6</v>
       </c>
@@ -11315,7 +11319,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="540" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
         <v>6</v>
       </c>
@@ -11335,7 +11339,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="541" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
         <v>6</v>
       </c>
@@ -11355,7 +11359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="542" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>6</v>
       </c>
@@ -11375,7 +11379,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="543" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>6</v>
       </c>
@@ -11395,7 +11399,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="544" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>6</v>
       </c>
@@ -11415,7 +11419,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="545" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
         <v>6</v>
       </c>
@@ -11435,7 +11439,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="546" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
         <v>6</v>
       </c>
@@ -11455,7 +11459,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="547" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>6</v>
       </c>
@@ -11475,7 +11479,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="548" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>6</v>
       </c>
@@ -11492,10 +11496,10 @@
         <v>0</v>
       </c>
       <c r="F548">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="549" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="549" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>6</v>
       </c>
@@ -11512,10 +11516,10 @@
         <v>1</v>
       </c>
       <c r="F549">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="550" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="550" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>6</v>
       </c>
@@ -11532,10 +11536,10 @@
         <v>2</v>
       </c>
       <c r="F550">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="551" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="551" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>6</v>
       </c>
@@ -11552,10 +11556,10 @@
         <v>3</v>
       </c>
       <c r="F551">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="552" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="552" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
         <v>6</v>
       </c>
@@ -11572,10 +11576,10 @@
         <v>4</v>
       </c>
       <c r="F552">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="553" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="553" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
         <v>6</v>
       </c>
@@ -11592,10 +11596,10 @@
         <v>5</v>
       </c>
       <c r="F553">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="554" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="554" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>6</v>
       </c>
@@ -11612,10 +11616,10 @@
         <v>6</v>
       </c>
       <c r="F554">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="555" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="555" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
         <v>6</v>
       </c>
@@ -11635,7 +11639,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="556" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
         <v>6</v>
       </c>
@@ -11655,7 +11659,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="557" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>6</v>
       </c>
@@ -11675,7 +11679,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="558" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>6</v>
       </c>
@@ -11695,7 +11699,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="559" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
         <v>6</v>
       </c>
@@ -11715,7 +11719,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="560" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>6</v>
       </c>
@@ -11735,7 +11739,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="561" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
         <v>6</v>
       </c>
@@ -11755,7 +11759,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="562" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>6</v>
       </c>
@@ -11775,7 +11779,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="563" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
         <v>6</v>
       </c>
@@ -11795,7 +11799,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="564" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
         <v>6</v>
       </c>
@@ -11815,7 +11819,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="565" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
         <v>6</v>
       </c>
@@ -11835,7 +11839,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="566" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
         <v>6</v>
       </c>
@@ -11855,7 +11859,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="567" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>6</v>
       </c>
@@ -11875,7 +11879,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="568" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>6</v>
       </c>
@@ -11895,7 +11899,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="569" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>6</v>
       </c>
@@ -11912,10 +11916,10 @@
         <v>0</v>
       </c>
       <c r="F569">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="570" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="570" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
         <v>6</v>
       </c>
@@ -11932,10 +11936,10 @@
         <v>1</v>
       </c>
       <c r="F570">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="571" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="571" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
         <v>6</v>
       </c>
@@ -11952,10 +11956,10 @@
         <v>2</v>
       </c>
       <c r="F571">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="572" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="572" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
         <v>6</v>
       </c>
@@ -11972,10 +11976,10 @@
         <v>3</v>
       </c>
       <c r="F572">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="573" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="573" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
         <v>6</v>
       </c>
@@ -11992,10 +11996,10 @@
         <v>4</v>
       </c>
       <c r="F573">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="574" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="574" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
         <v>6</v>
       </c>
@@ -12012,10 +12016,10 @@
         <v>5</v>
       </c>
       <c r="F574">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="575" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="575" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
         <v>6</v>
       </c>
@@ -12032,10 +12036,10 @@
         <v>6</v>
       </c>
       <c r="F575">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="576" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="576" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
         <v>6</v>
       </c>
@@ -12055,7 +12059,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="577" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
         <v>6</v>
       </c>
@@ -12075,7 +12079,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="578" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
         <v>6</v>
       </c>
@@ -12095,7 +12099,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="579" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
         <v>6</v>
       </c>
@@ -12115,7 +12119,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="580" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
         <v>6</v>
       </c>
@@ -12135,7 +12139,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="581" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
         <v>6</v>
       </c>
@@ -12155,7 +12159,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="582" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
         <v>6</v>
       </c>
@@ -12175,7 +12179,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="583" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
         <v>6</v>
       </c>
@@ -12195,7 +12199,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="584" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
         <v>6</v>
       </c>
@@ -12215,7 +12219,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="585" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
         <v>6</v>
       </c>
@@ -12235,7 +12239,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="586" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
         <v>6</v>
       </c>
@@ -12255,7 +12259,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="587" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
         <v>6</v>
       </c>
@@ -12275,7 +12279,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="588" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
         <v>6</v>
       </c>
@@ -12295,7 +12299,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="589" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
         <v>6</v>
       </c>
@@ -12315,7 +12319,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="590" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
         <v>6</v>
       </c>
@@ -12332,10 +12336,10 @@
         <v>0</v>
       </c>
       <c r="F590">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="591" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="591" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
         <v>6</v>
       </c>
@@ -12352,10 +12356,10 @@
         <v>1</v>
       </c>
       <c r="F591">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="592" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="592" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
         <v>6</v>
       </c>
@@ -12372,10 +12376,10 @@
         <v>2</v>
       </c>
       <c r="F592">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="593" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="593" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
         <v>6</v>
       </c>
@@ -12392,10 +12396,10 @@
         <v>3</v>
       </c>
       <c r="F593">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="594" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="594" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
         <v>6</v>
       </c>
@@ -12412,10 +12416,10 @@
         <v>4</v>
       </c>
       <c r="F594">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="595" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="595" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
         <v>6</v>
       </c>
@@ -12432,10 +12436,10 @@
         <v>5</v>
       </c>
       <c r="F595">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="596" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="596" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
         <v>6</v>
       </c>
@@ -12452,10 +12456,10 @@
         <v>6</v>
       </c>
       <c r="F596">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="597" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="597" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
         <v>6</v>
       </c>
@@ -12475,7 +12479,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="598" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
         <v>6</v>
       </c>
@@ -12495,7 +12499,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="599" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
         <v>6</v>
       </c>
@@ -12515,7 +12519,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="600" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
         <v>6</v>
       </c>
@@ -12535,7 +12539,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="601" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
         <v>6</v>
       </c>
@@ -12555,7 +12559,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="602" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
         <v>6</v>
       </c>
@@ -12575,7 +12579,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="603" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
         <v>6</v>
       </c>
@@ -12595,7 +12599,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="604" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
         <v>6</v>
       </c>
@@ -12615,7 +12619,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="605" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
         <v>6</v>
       </c>
@@ -12635,7 +12639,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="606" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
         <v>6</v>
       </c>
@@ -12655,7 +12659,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="607" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
         <v>6</v>
       </c>
@@ -12675,7 +12679,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="608" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
         <v>6</v>
       </c>
@@ -12695,7 +12699,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="609" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
         <v>6</v>
       </c>
@@ -12715,7 +12719,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="610" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
         <v>6</v>
       </c>
@@ -12735,7 +12739,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="611" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
         <v>6</v>
       </c>
@@ -12752,10 +12756,10 @@
         <v>0</v>
       </c>
       <c r="F611">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="612" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="612" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
         <v>6</v>
       </c>
@@ -12772,10 +12776,10 @@
         <v>1</v>
       </c>
       <c r="F612">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="613" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="613" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
         <v>6</v>
       </c>
@@ -12792,10 +12796,10 @@
         <v>2</v>
       </c>
       <c r="F613">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="614" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="614" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
         <v>6</v>
       </c>
@@ -12812,10 +12816,10 @@
         <v>3</v>
       </c>
       <c r="F614">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="615" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="615" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
         <v>6</v>
       </c>
@@ -12832,10 +12836,10 @@
         <v>4</v>
       </c>
       <c r="F615">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="616" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="616" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
         <v>6</v>
       </c>
@@ -12852,10 +12856,10 @@
         <v>5</v>
       </c>
       <c r="F616">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="617" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="617" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
         <v>6</v>
       </c>
@@ -12872,10 +12876,10 @@
         <v>6</v>
       </c>
       <c r="F617">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="618" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="618" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
         <v>6</v>
       </c>
@@ -12895,7 +12899,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="619" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
         <v>6</v>
       </c>
@@ -12915,7 +12919,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="620" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
         <v>6</v>
       </c>
@@ -12935,7 +12939,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="621" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
         <v>6</v>
       </c>
@@ -12955,7 +12959,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="622" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
         <v>6</v>
       </c>
@@ -12975,7 +12979,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="623" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
         <v>6</v>
       </c>
@@ -12995,7 +12999,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="624" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
         <v>6</v>
       </c>
@@ -13015,7 +13019,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="625" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
         <v>6</v>
       </c>
@@ -13035,7 +13039,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="626" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
         <v>6</v>
       </c>
@@ -13055,7 +13059,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="627" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
         <v>6</v>
       </c>
@@ -13075,7 +13079,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="628" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
         <v>6</v>
       </c>
@@ -13095,7 +13099,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="629" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
         <v>6</v>
       </c>
@@ -13115,7 +13119,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="630" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
         <v>6</v>
       </c>
@@ -13135,7 +13139,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="631" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
         <v>6</v>
       </c>
@@ -13155,7 +13159,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="632" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
         <v>6</v>
       </c>
@@ -13172,10 +13176,10 @@
         <v>0</v>
       </c>
       <c r="F632">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="633" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="633" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
         <v>6</v>
       </c>
@@ -13192,10 +13196,10 @@
         <v>1</v>
       </c>
       <c r="F633">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="634" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="634" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
         <v>6</v>
       </c>
@@ -13212,10 +13216,10 @@
         <v>2</v>
       </c>
       <c r="F634">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="635" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="635" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
         <v>6</v>
       </c>
@@ -13232,10 +13236,10 @@
         <v>3</v>
       </c>
       <c r="F635">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="636" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="636" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
         <v>6</v>
       </c>
@@ -13252,10 +13256,10 @@
         <v>4</v>
       </c>
       <c r="F636">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="637" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="637" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
         <v>6</v>
       </c>
@@ -13272,10 +13276,10 @@
         <v>5</v>
       </c>
       <c r="F637">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="638" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="638" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
         <v>6</v>
       </c>
@@ -13292,10 +13296,10 @@
         <v>6</v>
       </c>
       <c r="F638">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="639" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="639" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
         <v>6</v>
       </c>
@@ -13315,7 +13319,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="640" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
         <v>6</v>
       </c>
@@ -13335,7 +13339,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="641" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
         <v>6</v>
       </c>
@@ -13355,7 +13359,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="642" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
         <v>6</v>
       </c>
@@ -13375,7 +13379,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="643" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
         <v>6</v>
       </c>
@@ -13395,7 +13399,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="644" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
         <v>6</v>
       </c>
@@ -13415,7 +13419,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="645" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
         <v>6</v>
       </c>
@@ -13435,7 +13439,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="646" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
         <v>6</v>
       </c>
@@ -13455,7 +13459,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="647" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
         <v>6</v>
       </c>
@@ -13475,7 +13479,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="648" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
         <v>6</v>
       </c>
@@ -13495,7 +13499,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="649" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
         <v>6</v>
       </c>
@@ -13515,7 +13519,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="650" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
         <v>6</v>
       </c>
@@ -13535,7 +13539,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="651" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
         <v>6</v>
       </c>
@@ -13555,7 +13559,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="652" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
         <v>6</v>
       </c>
@@ -13575,7 +13579,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="653" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
         <v>6</v>
       </c>
@@ -13592,10 +13596,10 @@
         <v>0</v>
       </c>
       <c r="F653">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="654" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="654" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
         <v>6</v>
       </c>
@@ -13612,10 +13616,10 @@
         <v>1</v>
       </c>
       <c r="F654">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="655" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="655" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
         <v>6</v>
       </c>
@@ -13632,10 +13636,10 @@
         <v>2</v>
       </c>
       <c r="F655">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="656" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="656" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
         <v>6</v>
       </c>
@@ -13652,10 +13656,10 @@
         <v>3</v>
       </c>
       <c r="F656">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="657" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="657" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
         <v>6</v>
       </c>
@@ -13672,10 +13676,10 @@
         <v>4</v>
       </c>
       <c r="F657">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="658" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="658" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
         <v>6</v>
       </c>
@@ -13692,10 +13696,10 @@
         <v>5</v>
       </c>
       <c r="F658">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="659" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="659" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
         <v>6</v>
       </c>
@@ -13712,10 +13716,10 @@
         <v>6</v>
       </c>
       <c r="F659">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="660" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="660" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
         <v>6</v>
       </c>
@@ -13735,7 +13739,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="661" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
         <v>6</v>
       </c>
@@ -13755,7 +13759,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="662" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
         <v>6</v>
       </c>
@@ -13775,7 +13779,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="663" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
         <v>6</v>
       </c>
@@ -13795,7 +13799,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="664" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
         <v>6</v>
       </c>
@@ -13815,7 +13819,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="665" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
         <v>6</v>
       </c>
@@ -13835,7 +13839,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="666" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
         <v>6</v>
       </c>
@@ -13855,7 +13859,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="667" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
         <v>6</v>
       </c>
@@ -13875,7 +13879,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="668" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
         <v>6</v>
       </c>
@@ -13895,7 +13899,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="669" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
         <v>6</v>
       </c>
@@ -13915,7 +13919,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="670" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
         <v>6</v>
       </c>
@@ -13935,7 +13939,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="671" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
         <v>6</v>
       </c>
@@ -13955,7 +13959,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="672" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
         <v>6</v>
       </c>
@@ -13975,7 +13979,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="673" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
         <v>6</v>
       </c>
@@ -13995,7 +13999,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="674" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
         <v>6</v>
       </c>
@@ -14015,7 +14019,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="675" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
         <v>6</v>
       </c>
@@ -14035,7 +14039,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="676" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
         <v>6</v>
       </c>
@@ -14055,7 +14059,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="677" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
         <v>6</v>
       </c>
@@ -14075,7 +14079,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="678" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
         <v>6</v>
       </c>
@@ -14095,7 +14099,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="679" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
         <v>6</v>
       </c>
@@ -14115,7 +14119,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="680" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
         <v>6</v>
       </c>
@@ -14135,7 +14139,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="681" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
         <v>6</v>
       </c>
@@ -14155,7 +14159,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="682" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
         <v>6</v>
       </c>
@@ -14175,7 +14179,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="683" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
         <v>6</v>
       </c>
@@ -14195,7 +14199,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="684" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
         <v>6</v>
       </c>
@@ -14215,7 +14219,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="685" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
         <v>6</v>
       </c>
@@ -14235,7 +14239,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="686" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
         <v>6</v>
       </c>
@@ -14255,7 +14259,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="687" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
         <v>6</v>
       </c>
@@ -14275,7 +14279,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="688" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
         <v>6</v>
       </c>
@@ -14295,7 +14299,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="689" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
         <v>6</v>
       </c>
@@ -14315,7 +14319,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="690" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
         <v>6</v>
       </c>
@@ -14335,7 +14339,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="691" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
         <v>6</v>
       </c>
@@ -14355,7 +14359,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="692" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
         <v>6</v>
       </c>
@@ -14375,7 +14379,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="693" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
         <v>6</v>
       </c>
@@ -14395,7 +14399,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="694" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
         <v>6</v>
       </c>
@@ -14415,7 +14419,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="695" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
         <v>6</v>
       </c>
@@ -14435,7 +14439,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="696" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
         <v>6</v>
       </c>
@@ -14455,7 +14459,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="697" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
         <v>6</v>
       </c>
@@ -14475,7 +14479,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="698" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
         <v>6</v>
       </c>
@@ -14495,7 +14499,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="699" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
         <v>6</v>
       </c>
@@ -14515,7 +14519,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="700" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
         <v>6</v>
       </c>
@@ -14535,7 +14539,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="701" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
         <v>6</v>
       </c>
@@ -14555,7 +14559,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="702" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
         <v>6</v>
       </c>
@@ -14575,7 +14579,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="703" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
         <v>6</v>
       </c>
@@ -14595,7 +14599,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="704" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
         <v>6</v>
       </c>
@@ -14615,7 +14619,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="705" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
         <v>6</v>
       </c>
@@ -14636,10 +14640,10 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F673" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:F705" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:F19 A254:F271 A250:D250 F250 A296:F314 A292:D292 F292 A548:F565 A544:D544 F544 A23:F40 A20:D20 F20 A44:F62 A41:D41 F41 A212:F229 A209:D209 F209 A233:F249 A230:D230 F230 A251:D251 F251 A275:F291 A272:D272 F272 A293:D293 F293 A422:F439 A419:D419 F419 A443:F460 A440:D440 F440 A464:F482 A461:D461 F461 A545:D545 F545 A569:F588 A566:D566 F566 A632:F651 A629:D629 F629 A673:D673 A671:D671 F671 A21:D21 F21 A42:D42 F42 A65:F84 A63:D63 F63 A107:F126 A105:D105 F105 A149:F167 A147:D147 F147 A170:F189 A168:D168 F168 A210:D210 F210 A231:D231 F231 A252:D252 F252 A273:D273 F273 A294:D294 F294 A317:F335 A315:D315 F315 A338:F377 A336:D336 F336 A380:F418 A378:D378 F378 A420:D420 F420 A441:D441 F441 A462:D462 F462 A485:F503 A483:D483 F483 A506:F524 A504:D504 F504 A527:F543 A525:D525 F525 A546:D546 F546 A567:D567 F567 A611:F628 A609:D609 F609 A630:D630 F630 A672:D672 F672 A22:D22 F22 A43:D43 F43 A64:D64 F64 A86:F104 A85:D85 F85 A106:D106 F106 A128:F146 A127:D127 F127 A148:D148 F148 A169:D169 F169 A191:F208 A190:D190 F190 A211:D211 F211 A232:D232 F232 A253:D253 F253 A274:D274 F274 A295:D295 F295 A316:D316 F316 A337:D337 F337 A379:D379 F379 A421:D421 F421 A442:D442 F442 A463:D463 F463 A484:D484 F484 A505:D505 F505 A526:D526 F526 A547:D547 F547 A568:D568 F568 A590:F608 A589:D589 F589 A610:D610 F610 A631:D631 F631 A653:F670 A652:D652 F652 F673" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:C1 A255:C271 A250:C250 A297:C314 A292:C292 A549:C565 A544:C544 A24:C40 A20:C20 A45:C62 A41:C41 A213:C229 A209:C209 A234:C249 A230:C230 A251:C251 A276:C291 A272:C272 A293:C293 A423:C439 A419:C419 A444:C460 A440:C440 A465:C482 A461:C461 A545:C545 A570:C588 A566:C566 A633:C651 A629:C629 A673:C673 A671:C671 A21:C21 A42:C42 A66:C84 A63:C63 A108:C126 A105:C105 A150:C167 A147:C147 A171:C189 A168:C168 A210:C210 A231:C231 A252:C252 A273:C273 A294:C294 A318:C335 A315:C315 A339:C358 A336:C336 A381:C400 A378:C378 A420:C420 A441:C441 A462:C462 A486:C503 A483:C483 A507:C524 A504:C504 A528:C543 A525:C525 A546:C546 A567:C567 A612:C628 A609:C609 A630:C630 A672:C672 A22:C22 A43:C43 A64:C64 A87:C104 A85:C85 A106:C106 A129:C146 A127:C127 A148:C148 A169:C169 A192:C208 A190:C190 A211:C211 A232:C232 A253:C253 A274:C274 A295:C295 A316:C316 A337:C337 A379:C379 A421:C421 A442:C442 A463:C463 A484:C484 A505:C505 A526:C526 A547:C547 A568:C568 A591:C608 A589:C589 A610:C610 A631:C631 A654:C670 A652:C652 A3:C19 A2:C2 A23:C23 A44:C44 A65:C65 A86:C86 A107:C107 A128:C128 A149:C149 A170:C170 A191:C191 A212:C212 A233:C233 A254:C254 A275:C275 A296:C296 A317:C317 A338:C338 A360:C377 A359:C359 A380:C380 A402:C418 A401:C401 A422:C422 A443:C443 A464:C464 A485:C485 A506:C506 A527:C527 A548:C548 A569:C569 A590:C590 A611:C611 A632:C632 A653:C653" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>